--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33610,6 +33610,120 @@
         <v>563.2550000000001</v>
       </c>
     </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>11/10/2024</t>
+        </is>
+      </c>
+      <c r="B1747" t="n">
+        <v>549.1754166666666</v>
+      </c>
+      <c r="C1747" t="n">
+        <v>549.15</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>489.4129166666667</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>549.1900000000001</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>12/10/2024</t>
+        </is>
+      </c>
+      <c r="B1748" t="n">
+        <v>435.7679166666667</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>435.7474999999999</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>417.4683333333333</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>435.7866666666667</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>13/10/2024</t>
+        </is>
+      </c>
+      <c r="B1749" t="n">
+        <v>347.8445833333333</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>347.8187500000001</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>347.8308333333334</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>347.8575000000001</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>14/10/2024</t>
+        </is>
+      </c>
+      <c r="B1750" t="n">
+        <v>525.2058333333333</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>525.1758333333333</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>414.6966666666667</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>525.6620833333333</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="B1751" t="n">
+        <v>556.0424999999999</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>556.0091666666667</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>530.1066666666667</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>556.4699999999999</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>16/10/2024</t>
+        </is>
+      </c>
+      <c r="B1752" t="n">
+        <v>597.5433333333334</v>
+      </c>
+      <c r="C1752" t="n">
+        <v>597.5033333333333</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>597.5233333333334</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>597.55625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2121"/>
+  <dimension ref="A1:E2130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40735,6 +40735,177 @@
         <v>227.3383333333333</v>
       </c>
     </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="B2122" t="n">
+        <v>139.2604166666667</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>139.2579166666667</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>105.8404166666667</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>138.6183333333333</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="B2123" t="n">
+        <v>206.55375</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>206.5529166666667</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>162.445</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>206.4025</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="B2124" t="n">
+        <v>175.2579166666667</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>175.2575</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>130.9708333333334</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>175.1370833333333</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="B2125" t="n">
+        <v>218.2866666666667</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>218.285</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>132.0579166666667</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>214.3033333333333</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="B2126" t="n">
+        <v>218.8570833333332</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>218.8520833333333</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>181.3404166666666</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>218.7345833333333</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="B2127" t="n">
+        <v>203.22375</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>203.2183333333333</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>181.7291666666666</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>203.13125</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="B2128" t="n">
+        <v>317.2516666666667</v>
+      </c>
+      <c r="C2128" t="n">
+        <v>317.24625</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>264.7204166666667</v>
+      </c>
+      <c r="E2128" t="n">
+        <v>310.6279166666666</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="B2129" t="n">
+        <v>311.9820833333333</v>
+      </c>
+      <c r="C2129" t="n">
+        <v>311.9770833333334</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>260.6533333333334</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>300.5870833333333</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="B2130" t="n">
+        <v>317.33625</v>
+      </c>
+      <c r="C2130" t="n">
+        <v>317.33125</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>276.9333333333333</v>
+      </c>
+      <c r="E2130" t="n">
+        <v>317.3358333333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2171"/>
+  <dimension ref="A1:E2198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41685,6 +41685,519 @@
         <v>326.4612500000001</v>
       </c>
     </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="B2172" t="n">
+        <v>377.7608333333333</v>
+      </c>
+      <c r="C2172" t="n">
+        <v>377.7516666666667</v>
+      </c>
+      <c r="D2172" t="n">
+        <v>377.7549999999999</v>
+      </c>
+      <c r="E2172" t="n">
+        <v>377.7616666666666</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>11/12/2025</t>
+        </is>
+      </c>
+      <c r="B2173" t="n">
+        <v>314.2195833333333</v>
+      </c>
+      <c r="C2173" t="n">
+        <v>314.2108333333334</v>
+      </c>
+      <c r="D2173" t="n">
+        <v>314.2150000000001</v>
+      </c>
+      <c r="E2173" t="n">
+        <v>314.2208333333334</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="B2174" t="n">
+        <v>291.9570833333333</v>
+      </c>
+      <c r="C2174" t="n">
+        <v>291.9508333333334</v>
+      </c>
+      <c r="D2174" t="n">
+        <v>291.9516666666666</v>
+      </c>
+      <c r="E2174" t="n">
+        <v>291.9583333333333</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>13/12/2025</t>
+        </is>
+      </c>
+      <c r="B2175" t="n">
+        <v>273.2279166666667</v>
+      </c>
+      <c r="C2175" t="n">
+        <v>273.2225</v>
+      </c>
+      <c r="D2175" t="n">
+        <v>273.2245833333333</v>
+      </c>
+      <c r="E2175" t="n">
+        <v>273.2316666666667</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>14/12/2025</t>
+        </is>
+      </c>
+      <c r="B2176" t="n">
+        <v>220.1829166666666</v>
+      </c>
+      <c r="C2176" t="n">
+        <v>220.1770833333333</v>
+      </c>
+      <c r="D2176" t="n">
+        <v>220.1820833333333</v>
+      </c>
+      <c r="E2176" t="n">
+        <v>220.1875</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="B2177" t="n">
+        <v>284.6695833333333</v>
+      </c>
+      <c r="C2177" t="n">
+        <v>284.66625</v>
+      </c>
+      <c r="D2177" t="n">
+        <v>284.665</v>
+      </c>
+      <c r="E2177" t="n">
+        <v>284.6708333333333</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="B2178" t="n">
+        <v>277.8979166666667</v>
+      </c>
+      <c r="C2178" t="n">
+        <v>277.8908333333333</v>
+      </c>
+      <c r="D2178" t="n">
+        <v>277.8929166666666</v>
+      </c>
+      <c r="E2178" t="n">
+        <v>277.9</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="B2179" t="n">
+        <v>274.5920833333333</v>
+      </c>
+      <c r="C2179" t="n">
+        <v>274.58375</v>
+      </c>
+      <c r="D2179" t="n">
+        <v>274.5858333333334</v>
+      </c>
+      <c r="E2179" t="n">
+        <v>274.5941666666667</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>18/12/2025</t>
+        </is>
+      </c>
+      <c r="B2180" t="n">
+        <v>271.1275</v>
+      </c>
+      <c r="C2180" t="n">
+        <v>271.11875</v>
+      </c>
+      <c r="D2180" t="n">
+        <v>271.12125</v>
+      </c>
+      <c r="E2180" t="n">
+        <v>271.1291666666667</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="B2181" t="n">
+        <v>250.4425</v>
+      </c>
+      <c r="C2181" t="n">
+        <v>250.4429166666667</v>
+      </c>
+      <c r="D2181" t="n">
+        <v>250.4370833333334</v>
+      </c>
+      <c r="E2181" t="n">
+        <v>250.44625</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>20/12/2025</t>
+        </is>
+      </c>
+      <c r="B2182" t="n">
+        <v>155.6145833333333</v>
+      </c>
+      <c r="C2182" t="n">
+        <v>155.6145833333333</v>
+      </c>
+      <c r="D2182" t="n">
+        <v>155.6116666666667</v>
+      </c>
+      <c r="E2182" t="n">
+        <v>155.6174999999999</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>21/12/2025</t>
+        </is>
+      </c>
+      <c r="B2183" t="n">
+        <v>161.7720833333333</v>
+      </c>
+      <c r="C2183" t="n">
+        <v>161.7729166666666</v>
+      </c>
+      <c r="D2183" t="n">
+        <v>161.7675</v>
+      </c>
+      <c r="E2183" t="n">
+        <v>161.77375</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>22/12/2025</t>
+        </is>
+      </c>
+      <c r="B2184" t="n">
+        <v>231.3608333333333</v>
+      </c>
+      <c r="C2184" t="n">
+        <v>231.3633333333333</v>
+      </c>
+      <c r="D2184" t="n">
+        <v>231.3558333333333</v>
+      </c>
+      <c r="E2184" t="n">
+        <v>231.3629166666667</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>23/12/2025</t>
+        </is>
+      </c>
+      <c r="B2185" t="n">
+        <v>224.9225</v>
+      </c>
+      <c r="C2185" t="n">
+        <v>224.9266666666666</v>
+      </c>
+      <c r="D2185" t="n">
+        <v>224.5033333333333</v>
+      </c>
+      <c r="E2185" t="n">
+        <v>224.5120833333333</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>24/12/2025</t>
+        </is>
+      </c>
+      <c r="B2186" t="n">
+        <v>165.6383333333333</v>
+      </c>
+      <c r="C2186" t="n">
+        <v>165.6420833333333</v>
+      </c>
+      <c r="D2186" t="n">
+        <v>165.5675</v>
+      </c>
+      <c r="E2186" t="n">
+        <v>165.5733333333333</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>25/12/2025</t>
+        </is>
+      </c>
+      <c r="B2187" t="n">
+        <v>166.8529166666666</v>
+      </c>
+      <c r="C2187" t="n">
+        <v>166.8541666666666</v>
+      </c>
+      <c r="D2187" t="n">
+        <v>166.8491666666666</v>
+      </c>
+      <c r="E2187" t="n">
+        <v>166.8545833333333</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>26/12/2025</t>
+        </is>
+      </c>
+      <c r="B2188" t="n">
+        <v>201.39</v>
+      </c>
+      <c r="C2188" t="n">
+        <v>201.39125</v>
+      </c>
+      <c r="D2188" t="n">
+        <v>201.2133333333333</v>
+      </c>
+      <c r="E2188" t="n">
+        <v>201.2208333333333</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="B2189" t="n">
+        <v>156.5266666666666</v>
+      </c>
+      <c r="C2189" t="n">
+        <v>156.5241666666666</v>
+      </c>
+      <c r="D2189" t="n">
+        <v>156.5220833333333</v>
+      </c>
+      <c r="E2189" t="n">
+        <v>156.52875</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>28/12/2025</t>
+        </is>
+      </c>
+      <c r="B2190" t="n">
+        <v>156.4183333333333</v>
+      </c>
+      <c r="C2190" t="n">
+        <v>156.41375</v>
+      </c>
+      <c r="D2190" t="n">
+        <v>156.41375</v>
+      </c>
+      <c r="E2190" t="n">
+        <v>156.4208333333333</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="B2191" t="n">
+        <v>401.8783333333334</v>
+      </c>
+      <c r="C2191" t="n">
+        <v>401.8741666666667</v>
+      </c>
+      <c r="D2191" t="n">
+        <v>401.8745833333334</v>
+      </c>
+      <c r="E2191" t="n">
+        <v>401.8812500000001</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>30/12/2025</t>
+        </is>
+      </c>
+      <c r="B2192" t="n">
+        <v>206.83125</v>
+      </c>
+      <c r="C2192" t="n">
+        <v>206.8258333333333</v>
+      </c>
+      <c r="D2192" t="n">
+        <v>206.8295833333334</v>
+      </c>
+      <c r="E2192" t="n">
+        <v>206.8325</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>31/12/2025</t>
+        </is>
+      </c>
+      <c r="B2193" t="n">
+        <v>173.5120833333333</v>
+      </c>
+      <c r="C2193" t="n">
+        <v>173.5083333333333</v>
+      </c>
+      <c r="D2193" t="n">
+        <v>173.5070833333333</v>
+      </c>
+      <c r="E2193" t="n">
+        <v>173.5120833333334</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="B2194" t="n">
+        <v>150.3845833333333</v>
+      </c>
+      <c r="C2194" t="n">
+        <v>150.3808333333333</v>
+      </c>
+      <c r="D2194" t="n">
+        <v>150.3854166666666</v>
+      </c>
+      <c r="E2194" t="n">
+        <v>150.3854166666666</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="B2195" t="n">
+        <v>192.3604166666667</v>
+      </c>
+      <c r="C2195" t="n">
+        <v>192.3575</v>
+      </c>
+      <c r="D2195" t="n">
+        <v>192.3583333333333</v>
+      </c>
+      <c r="E2195" t="n">
+        <v>192.3625</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>03/01/2026</t>
+        </is>
+      </c>
+      <c r="B2196" t="n">
+        <v>139.8970833333333</v>
+      </c>
+      <c r="C2196" t="n">
+        <v>139.8929166666667</v>
+      </c>
+      <c r="D2196" t="n">
+        <v>139.8966666666667</v>
+      </c>
+      <c r="E2196" t="n">
+        <v>139.8970833333333</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="B2197" t="n">
+        <v>127.9879166666666</v>
+      </c>
+      <c r="C2197" t="n">
+        <v>127.9841666666666</v>
+      </c>
+      <c r="D2197" t="n">
+        <v>127.9883333333333</v>
+      </c>
+      <c r="E2197" t="n">
+        <v>127.98875</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="B2198" t="n">
+        <v>160.9116666666667</v>
+      </c>
+      <c r="C2198" t="n">
+        <v>160.91125</v>
+      </c>
+      <c r="D2198" t="n">
+        <v>160.9108333333333</v>
+      </c>
+      <c r="E2198" t="n">
+        <v>160.91125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2198"/>
+  <dimension ref="A1:E2219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42198,6 +42198,405 @@
         <v>160.91125</v>
       </c>
     </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="B2199" t="n">
+        <v>161.2370833333333</v>
+      </c>
+      <c r="C2199" t="n">
+        <v>161.23625</v>
+      </c>
+      <c r="D2199" t="n">
+        <v>161.2329166666667</v>
+      </c>
+      <c r="E2199" t="n">
+        <v>161.2383333333333</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="B2200" t="n">
+        <v>157.02</v>
+      </c>
+      <c r="C2200" t="n">
+        <v>157.0241666666667</v>
+      </c>
+      <c r="D2200" t="n">
+        <v>156.8654166666666</v>
+      </c>
+      <c r="E2200" t="n">
+        <v>156.8725</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="B2201" t="n">
+        <v>158.75375</v>
+      </c>
+      <c r="C2201" t="n">
+        <v>158.7575</v>
+      </c>
+      <c r="D2201" t="n">
+        <v>157.8095833333333</v>
+      </c>
+      <c r="E2201" t="n">
+        <v>157.8166666666666</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="B2202" t="n">
+        <v>159.3158333333333</v>
+      </c>
+      <c r="C2202" t="n">
+        <v>159.3225</v>
+      </c>
+      <c r="D2202" t="n">
+        <v>157.4929166666667</v>
+      </c>
+      <c r="E2202" t="n">
+        <v>157.50125</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="B2203" t="n">
+        <v>215.7466666666667</v>
+      </c>
+      <c r="C2203" t="n">
+        <v>215.7483333333334</v>
+      </c>
+      <c r="D2203" t="n">
+        <v>210.4708333333333</v>
+      </c>
+      <c r="E2203" t="n">
+        <v>210.69</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>11/01/2026</t>
+        </is>
+      </c>
+      <c r="B2204" t="n">
+        <v>205.135</v>
+      </c>
+      <c r="C2204" t="n">
+        <v>205.1341666666666</v>
+      </c>
+      <c r="D2204" t="n">
+        <v>203.7524999999999</v>
+      </c>
+      <c r="E2204" t="n">
+        <v>203.7583333333333</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="B2205" t="n">
+        <v>286.2187500000001</v>
+      </c>
+      <c r="C2205" t="n">
+        <v>286.2204166666667</v>
+      </c>
+      <c r="D2205" t="n">
+        <v>280.2295833333334</v>
+      </c>
+      <c r="E2205" t="n">
+        <v>280.2445833333334</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
+        </is>
+      </c>
+      <c r="B2206" t="n">
+        <v>284.9575</v>
+      </c>
+      <c r="C2206" t="n">
+        <v>285.0062500000001</v>
+      </c>
+      <c r="D2206" t="n">
+        <v>262.32625</v>
+      </c>
+      <c r="E2206" t="n">
+        <v>278.4629166666667</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>14/01/2026</t>
+        </is>
+      </c>
+      <c r="B2207" t="n">
+        <v>303.7495833333333</v>
+      </c>
+      <c r="C2207" t="n">
+        <v>305.0158333333333</v>
+      </c>
+      <c r="D2207" t="n">
+        <v>264.4320833333333</v>
+      </c>
+      <c r="E2207" t="n">
+        <v>284.0329166666667</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="B2208" t="n">
+        <v>299.1204166666666</v>
+      </c>
+      <c r="C2208" t="n">
+        <v>301.0595833333333</v>
+      </c>
+      <c r="D2208" t="n">
+        <v>282.4845833333334</v>
+      </c>
+      <c r="E2208" t="n">
+        <v>288.1116666666666</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="B2209" t="n">
+        <v>302.7025</v>
+      </c>
+      <c r="C2209" t="n">
+        <v>304.5741666666667</v>
+      </c>
+      <c r="D2209" t="n">
+        <v>289.2758333333333</v>
+      </c>
+      <c r="E2209" t="n">
+        <v>292.4254166666666</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="B2210" t="n">
+        <v>291.43</v>
+      </c>
+      <c r="C2210" t="n">
+        <v>291.4329166666666</v>
+      </c>
+      <c r="D2210" t="n">
+        <v>288.0354166666667</v>
+      </c>
+      <c r="E2210" t="n">
+        <v>288.04125</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>18/01/2026</t>
+        </is>
+      </c>
+      <c r="B2211" t="n">
+        <v>260.4633333333333</v>
+      </c>
+      <c r="C2211" t="n">
+        <v>260.4591666666667</v>
+      </c>
+      <c r="D2211" t="n">
+        <v>260.4608333333334</v>
+      </c>
+      <c r="E2211" t="n">
+        <v>260.4616666666666</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="B2212" t="n">
+        <v>329.0724999999999</v>
+      </c>
+      <c r="C2212" t="n">
+        <v>329.0658333333334</v>
+      </c>
+      <c r="D2212" t="n">
+        <v>329.0708333333334</v>
+      </c>
+      <c r="E2212" t="n">
+        <v>329.0654166666666</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="B2213" t="n">
+        <v>324.3058333333333</v>
+      </c>
+      <c r="C2213" t="n">
+        <v>324.2962499999999</v>
+      </c>
+      <c r="D2213" t="n">
+        <v>324.3012499999999</v>
+      </c>
+      <c r="E2213" t="n">
+        <v>324.2983333333333</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>21/01/2026</t>
+        </is>
+      </c>
+      <c r="B2214" t="n">
+        <v>324.3058333333333</v>
+      </c>
+      <c r="C2214" t="n">
+        <v>324.2962499999999</v>
+      </c>
+      <c r="D2214" t="n">
+        <v>324.3012499999999</v>
+      </c>
+      <c r="E2214" t="n">
+        <v>324.2983333333333</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="B2215" t="n">
+        <v>295.07625</v>
+      </c>
+      <c r="C2215" t="n">
+        <v>295.07625</v>
+      </c>
+      <c r="D2215" t="n">
+        <v>290.8991666666666</v>
+      </c>
+      <c r="E2215" t="n">
+        <v>290.9045833333333</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="B2216" t="n">
+        <v>294.3120833333333</v>
+      </c>
+      <c r="C2216" t="n">
+        <v>294.3170833333334</v>
+      </c>
+      <c r="D2216" t="n">
+        <v>289.0758333333333</v>
+      </c>
+      <c r="E2216" t="n">
+        <v>289.36625</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>24/01/2026</t>
+        </is>
+      </c>
+      <c r="B2217" t="n">
+        <v>216.2179166666667</v>
+      </c>
+      <c r="C2217" t="n">
+        <v>223.0804166666667</v>
+      </c>
+      <c r="D2217" t="n">
+        <v>171.1733333333333</v>
+      </c>
+      <c r="E2217" t="n">
+        <v>171.7929166666667</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>25/01/2026</t>
+        </is>
+      </c>
+      <c r="B2218" t="n">
+        <v>197.9983333333333</v>
+      </c>
+      <c r="C2218" t="n">
+        <v>199.07125</v>
+      </c>
+      <c r="D2218" t="n">
+        <v>191.59875</v>
+      </c>
+      <c r="E2218" t="n">
+        <v>191.6041666666667</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="B2219" t="n">
+        <v>290.6570833333333</v>
+      </c>
+      <c r="C2219" t="n">
+        <v>292.5870833333333</v>
+      </c>
+      <c r="D2219" t="n">
+        <v>276.4741666666667</v>
+      </c>
+      <c r="E2219" t="n">
+        <v>276.6987500000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2219"/>
+  <dimension ref="A1:E2227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42597,6 +42597,158 @@
         <v>276.6987500000001</v>
       </c>
     </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
+        </is>
+      </c>
+      <c r="B2220" t="n">
+        <v>282.8233333333333</v>
+      </c>
+      <c r="C2220" t="n">
+        <v>287.2595833333333</v>
+      </c>
+      <c r="D2220" t="n">
+        <v>267.7041666666667</v>
+      </c>
+      <c r="E2220" t="n">
+        <v>268.5208333333333</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="B2221" t="n">
+        <v>335.0183333333334</v>
+      </c>
+      <c r="C2221" t="n">
+        <v>337.01</v>
+      </c>
+      <c r="D2221" t="n">
+        <v>297.1879166666667</v>
+      </c>
+      <c r="E2221" t="n">
+        <v>297.1829166666666</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="B2222" t="n">
+        <v>316.1833333333333</v>
+      </c>
+      <c r="C2222" t="n">
+        <v>319.475</v>
+      </c>
+      <c r="D2222" t="n">
+        <v>294.5495833333333</v>
+      </c>
+      <c r="E2222" t="n">
+        <v>294.5479166666667</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="B2223" t="n">
+        <v>302.85</v>
+      </c>
+      <c r="C2223" t="n">
+        <v>303.0008333333333</v>
+      </c>
+      <c r="D2223" t="n">
+        <v>300.4191666666667</v>
+      </c>
+      <c r="E2223" t="n">
+        <v>300.415</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>31/01/2026</t>
+        </is>
+      </c>
+      <c r="B2224" t="n">
+        <v>301.8954166666667</v>
+      </c>
+      <c r="C2224" t="n">
+        <v>357.2854166666667</v>
+      </c>
+      <c r="D2224" t="n">
+        <v>301.8933333333334</v>
+      </c>
+      <c r="E2224" t="n">
+        <v>301.8908333333333</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="B2225" t="n">
+        <v>268.0766666666667</v>
+      </c>
+      <c r="C2225" t="n">
+        <v>268.0770833333333</v>
+      </c>
+      <c r="D2225" t="n">
+        <v>268.07625</v>
+      </c>
+      <c r="E2225" t="n">
+        <v>268.0745833333334</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="B2226" t="n">
+        <v>393.7404166666667</v>
+      </c>
+      <c r="C2226" t="n">
+        <v>394.4870833333333</v>
+      </c>
+      <c r="D2226" t="n">
+        <v>393.7375</v>
+      </c>
+      <c r="E2226" t="n">
+        <v>393.735</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B2227" t="n">
+        <v>457.2404166666666</v>
+      </c>
+      <c r="C2227" t="n">
+        <v>459.2208333333333</v>
+      </c>
+      <c r="D2227" t="n">
+        <v>457.2366666666667</v>
+      </c>
+      <c r="E2227" t="n">
+        <v>457.2316666666667</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2227"/>
+  <dimension ref="A1:E2261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42749,6 +42749,652 @@
         <v>457.2316666666667</v>
       </c>
     </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B2228" t="n">
+        <v>540.3112499999999</v>
+      </c>
+      <c r="C2228" t="n">
+        <v>542.3774999999999</v>
+      </c>
+      <c r="D2228" t="n">
+        <v>540.3108333333333</v>
+      </c>
+      <c r="E2228" t="n">
+        <v>540.3041666666667</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B2229" t="n">
+        <v>452.6354166666667</v>
+      </c>
+      <c r="C2229" t="n">
+        <v>455.6224999999999</v>
+      </c>
+      <c r="D2229" t="n">
+        <v>452.6366666666666</v>
+      </c>
+      <c r="E2229" t="n">
+        <v>452.6325</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B2230" t="n">
+        <v>374.115</v>
+      </c>
+      <c r="C2230" t="n">
+        <v>375.87375</v>
+      </c>
+      <c r="D2230" t="n">
+        <v>374.115</v>
+      </c>
+      <c r="E2230" t="n">
+        <v>374.1095833333334</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="B2231" t="n">
+        <v>407.6533333333334</v>
+      </c>
+      <c r="C2231" t="n">
+        <v>434.1633333333334</v>
+      </c>
+      <c r="D2231" t="n">
+        <v>407.6512499999999</v>
+      </c>
+      <c r="E2231" t="n">
+        <v>407.6500000000001</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>08/02/2026</t>
+        </is>
+      </c>
+      <c r="B2232" t="n">
+        <v>356.5766666666668</v>
+      </c>
+      <c r="C2232" t="n">
+        <v>356.5741666666666</v>
+      </c>
+      <c r="D2232" t="n">
+        <v>356.5795833333334</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>356.5766666666667</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="B2233" t="n">
+        <v>452.8125000000001</v>
+      </c>
+      <c r="C2233" t="n">
+        <v>453.0783333333334</v>
+      </c>
+      <c r="D2233" t="n">
+        <v>452.8091666666667</v>
+      </c>
+      <c r="E2233" t="n">
+        <v>452.8054166666666</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="B2234" t="n">
+        <v>443.2779166666666</v>
+      </c>
+      <c r="C2234" t="n">
+        <v>448.4824999999999</v>
+      </c>
+      <c r="D2234" t="n">
+        <v>443.2741666666668</v>
+      </c>
+      <c r="E2234" t="n">
+        <v>443.2733333333335</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="B2235" t="n">
+        <v>436.9679166666667</v>
+      </c>
+      <c r="C2235" t="n">
+        <v>446.5358333333334</v>
+      </c>
+      <c r="D2235" t="n">
+        <v>436.8466666666667</v>
+      </c>
+      <c r="E2235" t="n">
+        <v>436.8470833333333</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="B2236" t="n">
+        <v>413.5466666666667</v>
+      </c>
+      <c r="C2236" t="n">
+        <v>466.9945833333334</v>
+      </c>
+      <c r="D2236" t="n">
+        <v>401.26125</v>
+      </c>
+      <c r="E2236" t="n">
+        <v>401.2641666666668</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="B2237" t="n">
+        <v>407.3387499999999</v>
+      </c>
+      <c r="C2237" t="n">
+        <v>444.4091666666665</v>
+      </c>
+      <c r="D2237" t="n">
+        <v>402.3829166666667</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>402.3858333333334</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="B2238" t="n">
+        <v>280.54125</v>
+      </c>
+      <c r="C2238" t="n">
+        <v>375.5745833333333</v>
+      </c>
+      <c r="D2238" t="n">
+        <v>279.1308333333333</v>
+      </c>
+      <c r="E2238" t="n">
+        <v>279.1291666666667</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="B2239" t="n">
+        <v>255.0845833333333</v>
+      </c>
+      <c r="C2239" t="n">
+        <v>255.0895833333333</v>
+      </c>
+      <c r="D2239" t="n">
+        <v>252.3658333333334</v>
+      </c>
+      <c r="E2239" t="n">
+        <v>252.3666666666666</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="B2240" t="n">
+        <v>273.9924999999999</v>
+      </c>
+      <c r="C2240" t="n">
+        <v>390.8904166666667</v>
+      </c>
+      <c r="D2240" t="n">
+        <v>253.51375</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>253.515</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="B2241" t="n">
+        <v>277.7208333333332</v>
+      </c>
+      <c r="C2241" t="n">
+        <v>397.3241666666666</v>
+      </c>
+      <c r="D2241" t="n">
+        <v>256.8208333333333</v>
+      </c>
+      <c r="E2241" t="n">
+        <v>256.8204166666666</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="B2242" t="n">
+        <v>401.4233333333333</v>
+      </c>
+      <c r="C2242" t="n">
+        <v>423.4366666666667</v>
+      </c>
+      <c r="D2242" t="n">
+        <v>401.4191666666666</v>
+      </c>
+      <c r="E2242" t="n">
+        <v>401.4145833333334</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="B2243" t="n">
+        <v>453.8329166666667</v>
+      </c>
+      <c r="C2243" t="n">
+        <v>458.8770833333333</v>
+      </c>
+      <c r="D2243" t="n">
+        <v>453.8320833333333</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>453.8283333333333</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="B2244" t="n">
+        <v>422.3016666666667</v>
+      </c>
+      <c r="C2244" t="n">
+        <v>425.5666666666667</v>
+      </c>
+      <c r="D2244" t="n">
+        <v>422.2995833333335</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>422.2954166666668</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="B2245" t="n">
+        <v>336</v>
+      </c>
+      <c r="C2245" t="n">
+        <v>375.00625</v>
+      </c>
+      <c r="D2245" t="n">
+        <v>336.0004166666667</v>
+      </c>
+      <c r="E2245" t="n">
+        <v>335.9954166666666</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="B2246" t="n">
+        <v>286.5791666666667</v>
+      </c>
+      <c r="C2246" t="n">
+        <v>286.5804166666666</v>
+      </c>
+      <c r="D2246" t="n">
+        <v>286.58</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>286.57625</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="B2247" t="n">
+        <v>411.7966666666666</v>
+      </c>
+      <c r="C2247" t="n">
+        <v>411.8004166666666</v>
+      </c>
+      <c r="D2247" t="n">
+        <v>411.7958333333333</v>
+      </c>
+      <c r="E2247" t="n">
+        <v>411.7904166666665</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="B2248" t="n">
+        <v>394.5054166666666</v>
+      </c>
+      <c r="C2248" t="n">
+        <v>395.1012499999999</v>
+      </c>
+      <c r="D2248" t="n">
+        <v>394.50625</v>
+      </c>
+      <c r="E2248" t="n">
+        <v>394.5016666666666</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="B2249" t="n">
+        <v>417.0904166666667</v>
+      </c>
+      <c r="C2249" t="n">
+        <v>417.4683333333333</v>
+      </c>
+      <c r="D2249" t="n">
+        <v>417.0929166666667</v>
+      </c>
+      <c r="E2249" t="n">
+        <v>417.0858333333333</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="B2250" t="n">
+        <v>387.8229166666665</v>
+      </c>
+      <c r="C2250" t="n">
+        <v>391.9412499999999</v>
+      </c>
+      <c r="D2250" t="n">
+        <v>387.8241666666665</v>
+      </c>
+      <c r="E2250" t="n">
+        <v>387.8199999999999</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="B2251" t="n">
+        <v>376.2283333333334</v>
+      </c>
+      <c r="C2251" t="n">
+        <v>383.6741666666667</v>
+      </c>
+      <c r="D2251" t="n">
+        <v>375.7791666666667</v>
+      </c>
+      <c r="E2251" t="n">
+        <v>375.7745833333333</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="B2252" t="n">
+        <v>328.1329166666667</v>
+      </c>
+      <c r="C2252" t="n">
+        <v>341.1466666666666</v>
+      </c>
+      <c r="D2252" t="n">
+        <v>328.13375</v>
+      </c>
+      <c r="E2252" t="n">
+        <v>328.1283333333334</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="B2253" t="n">
+        <v>261.66125</v>
+      </c>
+      <c r="C2253" t="n">
+        <v>262.5108333333333</v>
+      </c>
+      <c r="D2253" t="n">
+        <v>261.6595833333333</v>
+      </c>
+      <c r="E2253" t="n">
+        <v>261.6541666666666</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="B2254" t="n">
+        <v>355.5591666666667</v>
+      </c>
+      <c r="C2254" t="n">
+        <v>440.8870833333334</v>
+      </c>
+      <c r="D2254" t="n">
+        <v>355.5604166666666</v>
+      </c>
+      <c r="E2254" t="n">
+        <v>355.5541666666666</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="B2255" t="n">
+        <v>371.1612500000001</v>
+      </c>
+      <c r="C2255" t="n">
+        <v>478.5674999999999</v>
+      </c>
+      <c r="D2255" t="n">
+        <v>371.1604166666667</v>
+      </c>
+      <c r="E2255" t="n">
+        <v>371.1533333333333</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="B2256" t="n">
+        <v>336.1516666666666</v>
+      </c>
+      <c r="C2256" t="n">
+        <v>487.4304166666668</v>
+      </c>
+      <c r="D2256" t="n">
+        <v>321.5824999999999</v>
+      </c>
+      <c r="E2256" t="n">
+        <v>321.5758333333333</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B2257" t="n">
+        <v>347.1216666666666</v>
+      </c>
+      <c r="C2257" t="n">
+        <v>498.6983333333333</v>
+      </c>
+      <c r="D2257" t="n">
+        <v>243.0254166666667</v>
+      </c>
+      <c r="E2257" t="n">
+        <v>243.0191666666666</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="B2258" t="n">
+        <v>379.11375</v>
+      </c>
+      <c r="C2258" t="n">
+        <v>520.36375</v>
+      </c>
+      <c r="D2258" t="n">
+        <v>179.37375</v>
+      </c>
+      <c r="E2258" t="n">
+        <v>179.3704166666667</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="B2259" t="n">
+        <v>287.0975</v>
+      </c>
+      <c r="C2259" t="n">
+        <v>594.8204166666666</v>
+      </c>
+      <c r="D2259" t="n">
+        <v>109.41625</v>
+      </c>
+      <c r="E2259" t="n">
+        <v>109.4120833333333</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>08/03/2026</t>
+        </is>
+      </c>
+      <c r="B2260" t="n">
+        <v>235.575</v>
+      </c>
+      <c r="C2260" t="n">
+        <v>332.4716666666666</v>
+      </c>
+      <c r="D2260" t="n">
+        <v>145.9958333333333</v>
+      </c>
+      <c r="E2260" t="n">
+        <v>145.9920833333333</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="B2261" t="n">
+        <v>354.0674999999999</v>
+      </c>
+      <c r="C2261" t="n">
+        <v>509.6979166666666</v>
+      </c>
+      <c r="D2261" t="n">
+        <v>283.9508333333333</v>
+      </c>
+      <c r="E2261" t="n">
+        <v>283.9445833333332</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/testepld.xlsx
+++ b/assets/testepld.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2261"/>
+  <dimension ref="A1:E2227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42749,652 +42749,6 @@
         <v>457.2316666666667</v>
       </c>
     </row>
-    <row r="2228">
-      <c r="A2228" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
-        </is>
-      </c>
-      <c r="B2228" t="n">
-        <v>540.3112499999999</v>
-      </c>
-      <c r="C2228" t="n">
-        <v>542.3774999999999</v>
-      </c>
-      <c r="D2228" t="n">
-        <v>540.3108333333333</v>
-      </c>
-      <c r="E2228" t="n">
-        <v>540.3041666666667</v>
-      </c>
-    </row>
-    <row r="2229">
-      <c r="A2229" t="inlineStr">
-        <is>
-          <t>05/02/2026</t>
-        </is>
-      </c>
-      <c r="B2229" t="n">
-        <v>452.6354166666667</v>
-      </c>
-      <c r="C2229" t="n">
-        <v>455.6224999999999</v>
-      </c>
-      <c r="D2229" t="n">
-        <v>452.6366666666666</v>
-      </c>
-      <c r="E2229" t="n">
-        <v>452.6325</v>
-      </c>
-    </row>
-    <row r="2230">
-      <c r="A2230" t="inlineStr">
-        <is>
-          <t>06/02/2026</t>
-        </is>
-      </c>
-      <c r="B2230" t="n">
-        <v>374.115</v>
-      </c>
-      <c r="C2230" t="n">
-        <v>375.87375</v>
-      </c>
-      <c r="D2230" t="n">
-        <v>374.115</v>
-      </c>
-      <c r="E2230" t="n">
-        <v>374.1095833333334</v>
-      </c>
-    </row>
-    <row r="2231">
-      <c r="A2231" t="inlineStr">
-        <is>
-          <t>07/02/2026</t>
-        </is>
-      </c>
-      <c r="B2231" t="n">
-        <v>407.6533333333334</v>
-      </c>
-      <c r="C2231" t="n">
-        <v>434.1633333333334</v>
-      </c>
-      <c r="D2231" t="n">
-        <v>407.6512499999999</v>
-      </c>
-      <c r="E2231" t="n">
-        <v>407.6500000000001</v>
-      </c>
-    </row>
-    <row r="2232">
-      <c r="A2232" t="inlineStr">
-        <is>
-          <t>08/02/2026</t>
-        </is>
-      </c>
-      <c r="B2232" t="n">
-        <v>356.5766666666668</v>
-      </c>
-      <c r="C2232" t="n">
-        <v>356.5741666666666</v>
-      </c>
-      <c r="D2232" t="n">
-        <v>356.5795833333334</v>
-      </c>
-      <c r="E2232" t="n">
-        <v>356.5766666666667</v>
-      </c>
-    </row>
-    <row r="2233">
-      <c r="A2233" t="inlineStr">
-        <is>
-          <t>09/02/2026</t>
-        </is>
-      </c>
-      <c r="B2233" t="n">
-        <v>452.8125000000001</v>
-      </c>
-      <c r="C2233" t="n">
-        <v>453.0783333333334</v>
-      </c>
-      <c r="D2233" t="n">
-        <v>452.8091666666667</v>
-      </c>
-      <c r="E2233" t="n">
-        <v>452.8054166666666</v>
-      </c>
-    </row>
-    <row r="2234">
-      <c r="A2234" t="inlineStr">
-        <is>
-          <t>10/02/2026</t>
-        </is>
-      </c>
-      <c r="B2234" t="n">
-        <v>443.2779166666666</v>
-      </c>
-      <c r="C2234" t="n">
-        <v>448.4824999999999</v>
-      </c>
-      <c r="D2234" t="n">
-        <v>443.2741666666668</v>
-      </c>
-      <c r="E2234" t="n">
-        <v>443.2733333333335</v>
-      </c>
-    </row>
-    <row r="2235">
-      <c r="A2235" t="inlineStr">
-        <is>
-          <t>11/02/2026</t>
-        </is>
-      </c>
-      <c r="B2235" t="n">
-        <v>436.9679166666667</v>
-      </c>
-      <c r="C2235" t="n">
-        <v>446.5358333333334</v>
-      </c>
-      <c r="D2235" t="n">
-        <v>436.8466666666667</v>
-      </c>
-      <c r="E2235" t="n">
-        <v>436.8470833333333</v>
-      </c>
-    </row>
-    <row r="2236">
-      <c r="A2236" t="inlineStr">
-        <is>
-          <t>12/02/2026</t>
-        </is>
-      </c>
-      <c r="B2236" t="n">
-        <v>413.5466666666667</v>
-      </c>
-      <c r="C2236" t="n">
-        <v>466.9945833333334</v>
-      </c>
-      <c r="D2236" t="n">
-        <v>401.26125</v>
-      </c>
-      <c r="E2236" t="n">
-        <v>401.2641666666668</v>
-      </c>
-    </row>
-    <row r="2237">
-      <c r="A2237" t="inlineStr">
-        <is>
-          <t>13/02/2026</t>
-        </is>
-      </c>
-      <c r="B2237" t="n">
-        <v>407.3387499999999</v>
-      </c>
-      <c r="C2237" t="n">
-        <v>444.4091666666665</v>
-      </c>
-      <c r="D2237" t="n">
-        <v>402.3829166666667</v>
-      </c>
-      <c r="E2237" t="n">
-        <v>402.3858333333334</v>
-      </c>
-    </row>
-    <row r="2238">
-      <c r="A2238" t="inlineStr">
-        <is>
-          <t>14/02/2026</t>
-        </is>
-      </c>
-      <c r="B2238" t="n">
-        <v>280.54125</v>
-      </c>
-      <c r="C2238" t="n">
-        <v>375.5745833333333</v>
-      </c>
-      <c r="D2238" t="n">
-        <v>279.1308333333333</v>
-      </c>
-      <c r="E2238" t="n">
-        <v>279.1291666666667</v>
-      </c>
-    </row>
-    <row r="2239">
-      <c r="A2239" t="inlineStr">
-        <is>
-          <t>15/02/2026</t>
-        </is>
-      </c>
-      <c r="B2239" t="n">
-        <v>255.0845833333333</v>
-      </c>
-      <c r="C2239" t="n">
-        <v>255.0895833333333</v>
-      </c>
-      <c r="D2239" t="n">
-        <v>252.3658333333334</v>
-      </c>
-      <c r="E2239" t="n">
-        <v>252.3666666666666</v>
-      </c>
-    </row>
-    <row r="2240">
-      <c r="A2240" t="inlineStr">
-        <is>
-          <t>16/02/2026</t>
-        </is>
-      </c>
-      <c r="B2240" t="n">
-        <v>273.9924999999999</v>
-      </c>
-      <c r="C2240" t="n">
-        <v>390.8904166666667</v>
-      </c>
-      <c r="D2240" t="n">
-        <v>253.51375</v>
-      </c>
-      <c r="E2240" t="n">
-        <v>253.515</v>
-      </c>
-    </row>
-    <row r="2241">
-      <c r="A2241" t="inlineStr">
-        <is>
-          <t>17/02/2026</t>
-        </is>
-      </c>
-      <c r="B2241" t="n">
-        <v>277.7208333333332</v>
-      </c>
-      <c r="C2241" t="n">
-        <v>397.3241666666666</v>
-      </c>
-      <c r="D2241" t="n">
-        <v>256.8208333333333</v>
-      </c>
-      <c r="E2241" t="n">
-        <v>256.8204166666666</v>
-      </c>
-    </row>
-    <row r="2242">
-      <c r="A2242" t="inlineStr">
-        <is>
-          <t>18/02/2026</t>
-        </is>
-      </c>
-      <c r="B2242" t="n">
-        <v>401.4233333333333</v>
-      </c>
-      <c r="C2242" t="n">
-        <v>423.4366666666667</v>
-      </c>
-      <c r="D2242" t="n">
-        <v>401.4191666666666</v>
-      </c>
-      <c r="E2242" t="n">
-        <v>401.4145833333334</v>
-      </c>
-    </row>
-    <row r="2243">
-      <c r="A2243" t="inlineStr">
-        <is>
-          <t>19/02/2026</t>
-        </is>
-      </c>
-      <c r="B2243" t="n">
-        <v>453.8329166666667</v>
-      </c>
-      <c r="C2243" t="n">
-        <v>458.8770833333333</v>
-      </c>
-      <c r="D2243" t="n">
-        <v>453.8320833333333</v>
-      </c>
-      <c r="E2243" t="n">
-        <v>453.8283333333333</v>
-      </c>
-    </row>
-    <row r="2244">
-      <c r="A2244" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-      <c r="B2244" t="n">
-        <v>422.3016666666667</v>
-      </c>
-      <c r="C2244" t="n">
-        <v>425.5666666666667</v>
-      </c>
-      <c r="D2244" t="n">
-        <v>422.2995833333335</v>
-      </c>
-      <c r="E2244" t="n">
-        <v>422.2954166666668</v>
-      </c>
-    </row>
-    <row r="2245">
-      <c r="A2245" t="inlineStr">
-        <is>
-          <t>21/02/2026</t>
-        </is>
-      </c>
-      <c r="B2245" t="n">
-        <v>336</v>
-      </c>
-      <c r="C2245" t="n">
-        <v>375.00625</v>
-      </c>
-      <c r="D2245" t="n">
-        <v>336.0004166666667</v>
-      </c>
-      <c r="E2245" t="n">
-        <v>335.9954166666666</v>
-      </c>
-    </row>
-    <row r="2246">
-      <c r="A2246" t="inlineStr">
-        <is>
-          <t>22/02/2026</t>
-        </is>
-      </c>
-      <c r="B2246" t="n">
-        <v>286.5791666666667</v>
-      </c>
-      <c r="C2246" t="n">
-        <v>286.5804166666666</v>
-      </c>
-      <c r="D2246" t="n">
-        <v>286.58</v>
-      </c>
-      <c r="E2246" t="n">
-        <v>286.57625</v>
-      </c>
-    </row>
-    <row r="2247">
-      <c r="A2247" t="inlineStr">
-        <is>
-          <t>23/02/2026</t>
-        </is>
-      </c>
-      <c r="B2247" t="n">
-        <v>411.7966666666666</v>
-      </c>
-      <c r="C2247" t="n">
-        <v>411.8004166666666</v>
-      </c>
-      <c r="D2247" t="n">
-        <v>411.7958333333333</v>
-      </c>
-      <c r="E2247" t="n">
-        <v>411.7904166666665</v>
-      </c>
-    </row>
-    <row r="2248">
-      <c r="A2248" t="inlineStr">
-        <is>
-          <t>24/02/2026</t>
-        </is>
-      </c>
-      <c r="B2248" t="n">
-        <v>394.5054166666666</v>
-      </c>
-      <c r="C2248" t="n">
-        <v>395.1012499999999</v>
-      </c>
-      <c r="D2248" t="n">
-        <v>394.50625</v>
-      </c>
-      <c r="E2248" t="n">
-        <v>394.5016666666666</v>
-      </c>
-    </row>
-    <row r="2249">
-      <c r="A2249" t="inlineStr">
-        <is>
-          <t>25/02/2026</t>
-        </is>
-      </c>
-      <c r="B2249" t="n">
-        <v>417.0904166666667</v>
-      </c>
-      <c r="C2249" t="n">
-        <v>417.4683333333333</v>
-      </c>
-      <c r="D2249" t="n">
-        <v>417.0929166666667</v>
-      </c>
-      <c r="E2249" t="n">
-        <v>417.0858333333333</v>
-      </c>
-    </row>
-    <row r="2250">
-      <c r="A2250" t="inlineStr">
-        <is>
-          <t>26/02/2026</t>
-        </is>
-      </c>
-      <c r="B2250" t="n">
-        <v>387.8229166666665</v>
-      </c>
-      <c r="C2250" t="n">
-        <v>391.9412499999999</v>
-      </c>
-      <c r="D2250" t="n">
-        <v>387.8241666666665</v>
-      </c>
-      <c r="E2250" t="n">
-        <v>387.8199999999999</v>
-      </c>
-    </row>
-    <row r="2251">
-      <c r="A2251" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="B2251" t="n">
-        <v>376.2283333333334</v>
-      </c>
-      <c r="C2251" t="n">
-        <v>383.6741666666667</v>
-      </c>
-      <c r="D2251" t="n">
-        <v>375.7791666666667</v>
-      </c>
-      <c r="E2251" t="n">
-        <v>375.7745833333333</v>
-      </c>
-    </row>
-    <row r="2252">
-      <c r="A2252" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
-      <c r="B2252" t="n">
-        <v>328.1329166666667</v>
-      </c>
-      <c r="C2252" t="n">
-        <v>341.1466666666666</v>
-      </c>
-      <c r="D2252" t="n">
-        <v>328.13375</v>
-      </c>
-      <c r="E2252" t="n">
-        <v>328.1283333333334</v>
-      </c>
-    </row>
-    <row r="2253">
-      <c r="A2253" t="inlineStr">
-        <is>
-          <t>01/03/2026</t>
-        </is>
-      </c>
-      <c r="B2253" t="n">
-        <v>261.66125</v>
-      </c>
-      <c r="C2253" t="n">
-        <v>262.5108333333333</v>
-      </c>
-      <c r="D2253" t="n">
-        <v>261.6595833333333</v>
-      </c>
-      <c r="E2253" t="n">
-        <v>261.6541666666666</v>
-      </c>
-    </row>
-    <row r="2254">
-      <c r="A2254" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
-      </c>
-      <c r="B2254" t="n">
-        <v>355.5591666666667</v>
-      </c>
-      <c r="C2254" t="n">
-        <v>440.8870833333334</v>
-      </c>
-      <c r="D2254" t="n">
-        <v>355.5604166666666</v>
-      </c>
-      <c r="E2254" t="n">
-        <v>355.5541666666666</v>
-      </c>
-    </row>
-    <row r="2255">
-      <c r="A2255" t="inlineStr">
-        <is>
-          <t>03/03/2026</t>
-        </is>
-      </c>
-      <c r="B2255" t="n">
-        <v>371.1612500000001</v>
-      </c>
-      <c r="C2255" t="n">
-        <v>478.5674999999999</v>
-      </c>
-      <c r="D2255" t="n">
-        <v>371.1604166666667</v>
-      </c>
-      <c r="E2255" t="n">
-        <v>371.1533333333333</v>
-      </c>
-    </row>
-    <row r="2256">
-      <c r="A2256" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="B2256" t="n">
-        <v>336.1516666666666</v>
-      </c>
-      <c r="C2256" t="n">
-        <v>487.4304166666668</v>
-      </c>
-      <c r="D2256" t="n">
-        <v>321.5824999999999</v>
-      </c>
-      <c r="E2256" t="n">
-        <v>321.5758333333333</v>
-      </c>
-    </row>
-    <row r="2257">
-      <c r="A2257" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="B2257" t="n">
-        <v>347.1216666666666</v>
-      </c>
-      <c r="C2257" t="n">
-        <v>498.6983333333333</v>
-      </c>
-      <c r="D2257" t="n">
-        <v>243.0254166666667</v>
-      </c>
-      <c r="E2257" t="n">
-        <v>243.0191666666666</v>
-      </c>
-    </row>
-    <row r="2258">
-      <c r="A2258" t="inlineStr">
-        <is>
-          <t>06/03/2026</t>
-        </is>
-      </c>
-      <c r="B2258" t="n">
-        <v>379.11375</v>
-      </c>
-      <c r="C2258" t="n">
-        <v>520.36375</v>
-      </c>
-      <c r="D2258" t="n">
-        <v>179.37375</v>
-      </c>
-      <c r="E2258" t="n">
-        <v>179.3704166666667</v>
-      </c>
-    </row>
-    <row r="2259">
-      <c r="A2259" t="inlineStr">
-        <is>
-          <t>07/03/2026</t>
-        </is>
-      </c>
-      <c r="B2259" t="n">
-        <v>287.0975</v>
-      </c>
-      <c r="C2259" t="n">
-        <v>594.8204166666666</v>
-      </c>
-      <c r="D2259" t="n">
-        <v>109.41625</v>
-      </c>
-      <c r="E2259" t="n">
-        <v>109.4120833333333</v>
-      </c>
-    </row>
-    <row r="2260">
-      <c r="A2260" t="inlineStr">
-        <is>
-          <t>08/03/2026</t>
-        </is>
-      </c>
-      <c r="B2260" t="n">
-        <v>235.575</v>
-      </c>
-      <c r="C2260" t="n">
-        <v>332.4716666666666</v>
-      </c>
-      <c r="D2260" t="n">
-        <v>145.9958333333333</v>
-      </c>
-      <c r="E2260" t="n">
-        <v>145.9920833333333</v>
-      </c>
-    </row>
-    <row r="2261">
-      <c r="A2261" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="B2261" t="n">
-        <v>354.0674999999999</v>
-      </c>
-      <c r="C2261" t="n">
-        <v>509.6979166666666</v>
-      </c>
-      <c r="D2261" t="n">
-        <v>283.9508333333333</v>
-      </c>
-      <c r="E2261" t="n">
-        <v>283.9445833333332</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
